--- a/outputs/per-fund/vc-investments-framework-ventures.xlsx
+++ b/outputs/per-fund/vc-investments-framework-ventures.xlsx
@@ -706,7 +706,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Only Framework Ventures. The full overview with all twenty funds is in vc-investments-full.xlsx.</t>
+          <t>Only Framework Ventures. The full overview with all 59 funds is in vc-investments-full.xlsx.</t>
         </is>
       </c>
     </row>
@@ -862,7 +862,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>The twenty funds, with control totals per external source.</t>
+          <t>The 59 funds, with control totals per external source.</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>One row per company in which at least one of the twenty funds invested.</t>
+          <t>One row per company in which at least one of these 59 funds invested.</t>
         </is>
       </c>
     </row>
@@ -23685,11 +23685,11 @@
         <v>1</v>
       </c>
       <c r="K6" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L6" s="5" t="inlineStr">
         <is>
-          <t>framework-ventures, maven11</t>
+          <t>framework-ventures, maven11, parafi-capital</t>
         </is>
       </c>
       <c r="M6" s="7" t="inlineStr">
@@ -23748,11 +23748,11 @@
         <v>1</v>
       </c>
       <c r="K7" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L7" s="5" t="inlineStr">
         <is>
-          <t>coinbase-ventures, framework-ventures</t>
+          <t>coinbase-ventures, coinfund, framework-ventures</t>
         </is>
       </c>
       <c r="M7" s="7" t="inlineStr">
@@ -23811,11 +23811,11 @@
         <v>1</v>
       </c>
       <c r="K8" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L8" s="5" t="inlineStr">
         <is>
-          <t>framework-ventures, pantera</t>
+          <t>cms-holdings, framework-ventures, pantera</t>
         </is>
       </c>
       <c r="M8" s="7" t="inlineStr">
@@ -23874,11 +23874,11 @@
         <v>1</v>
       </c>
       <c r="K9" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L9" s="5" t="inlineStr">
         <is>
-          <t>coinbase-ventures, electric-capital, framework-ventures, robot-ventures</t>
+          <t>coinbase-ventures, digital-currency-group, electric-capital, framework-ventures, robot-ventures</t>
         </is>
       </c>
       <c r="M9" s="7" t="inlineStr">
@@ -23937,11 +23937,11 @@
         <v>3</v>
       </c>
       <c r="K10" s="6" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="L10" s="5" t="inlineStr">
         <is>
-          <t>coinbase-ventures, framework-ventures, pantera</t>
+          <t>alameda-research, cms-holdings, coinbase-ventures, framework-ventures, galaxy-digital, iosg-ventures, longhash-ventures, pantera, yzi-labs</t>
         </is>
       </c>
       <c r="M10" s="7" t="inlineStr">
@@ -24000,11 +24000,11 @@
         <v>0</v>
       </c>
       <c r="K11" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L11" s="5" t="inlineStr">
         <is>
-          <t>framework-ventures</t>
+          <t>alameda-research, framework-ventures, mechanism-capital, spartan-group</t>
         </is>
       </c>
       <c r="M11" s="7" t="inlineStr">
@@ -24059,11 +24059,11 @@
         <v>0</v>
       </c>
       <c r="K12" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L12" s="5" t="inlineStr">
         <is>
-          <t>framework-ventures</t>
+          <t>alameda-research, framework-ventures, mechanism-capital</t>
         </is>
       </c>
       <c r="M12" s="7" t="inlineStr">
@@ -24185,11 +24185,11 @@
         <v>0</v>
       </c>
       <c r="K14" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L14" s="5" t="inlineStr">
         <is>
-          <t>a16z-crypto, coinbase-ventures, framework-ventures</t>
+          <t>a16z-crypto, coinbase-ventures, framework-ventures, parafi-capital</t>
         </is>
       </c>
       <c r="M14" s="7" t="inlineStr">
@@ -24248,11 +24248,11 @@
         <v>1</v>
       </c>
       <c r="K15" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L15" s="5" t="inlineStr">
         <is>
-          <t>delphi-ventures, framework-ventures</t>
+          <t>delphi-ventures, framework-ventures, iosg-ventures</t>
         </is>
       </c>
       <c r="M15" s="7" t="inlineStr">
@@ -24374,11 +24374,11 @@
         <v>0</v>
       </c>
       <c r="K17" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L17" s="5" t="inlineStr">
         <is>
-          <t>framework-ventures</t>
+          <t>framework-ventures, galaxy-digital</t>
         </is>
       </c>
       <c r="M17" s="7" t="inlineStr">
@@ -24437,11 +24437,11 @@
         <v>0</v>
       </c>
       <c r="K18" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L18" s="5" t="inlineStr">
         <is>
-          <t>framework-ventures</t>
+          <t>framework-ventures, mechanism-capital, spartan-group</t>
         </is>
       </c>
       <c r="M18" s="7" t="inlineStr">
@@ -24559,11 +24559,11 @@
         <v>3</v>
       </c>
       <c r="K20" s="6" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L20" s="5" t="inlineStr">
         <is>
-          <t>delphi-ventures, framework-ventures</t>
+          <t>blockchain-capital, cms-holdings, coinfund, delphi-ventures, framework-ventures, mechanism-capital</t>
         </is>
       </c>
       <c r="M20" s="7" t="inlineStr">
@@ -24622,11 +24622,11 @@
         <v>0</v>
       </c>
       <c r="K21" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L21" s="5" t="inlineStr">
         <is>
-          <t>framework-ventures</t>
+          <t>blockchain-capital, coinfund, framework-ventures</t>
         </is>
       </c>
       <c r="M21" s="7" t="inlineStr">
@@ -24685,11 +24685,11 @@
         <v>0</v>
       </c>
       <c r="K22" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L22" s="5" t="inlineStr">
         <is>
-          <t>framework-ventures, pantera</t>
+          <t>framework-ventures, hashkey-capital, pantera, sevenx-ventures</t>
         </is>
       </c>
       <c r="M22" s="7" t="inlineStr">
@@ -24809,11 +24809,11 @@
         <v>2</v>
       </c>
       <c r="K24" s="6" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L24" s="5" t="inlineStr">
         <is>
-          <t>dragonfly, framework-ventures</t>
+          <t>cms-holdings, dragonfly, framework-ventures, hashed, longhash-ventures, parafi-capital</t>
         </is>
       </c>
       <c r="M24" s="7" t="inlineStr">
@@ -24872,11 +24872,11 @@
         <v>0</v>
       </c>
       <c r="K25" s="6" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L25" s="5" t="inlineStr">
         <is>
-          <t>coinbase-ventures, electric-capital, framework-ventures, lemniscap, semantic-ventures</t>
+          <t>coinbase-ventures, coinfund, electric-capital, framework-ventures, hypersphere, lemniscap, semantic-ventures</t>
         </is>
       </c>
       <c r="M25" s="7" t="inlineStr">
@@ -24935,11 +24935,11 @@
         <v>1</v>
       </c>
       <c r="K26" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L26" s="5" t="inlineStr">
         <is>
-          <t>framework-ventures, paradigm</t>
+          <t>alliance-dao, cms-holdings, framework-ventures, paradigm</t>
         </is>
       </c>
       <c r="M26" s="7" t="inlineStr">
@@ -24998,11 +24998,11 @@
         <v>1</v>
       </c>
       <c r="K27" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L27" s="5" t="inlineStr">
         <is>
-          <t>framework-ventures</t>
+          <t>alliance-dao, framework-ventures</t>
         </is>
       </c>
       <c r="M27" s="7" t="inlineStr">
@@ -25057,11 +25057,11 @@
         <v>0</v>
       </c>
       <c r="K28" s="6" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L28" s="5" t="inlineStr">
         <is>
-          <t>framework-ventures, pantera</t>
+          <t>alameda-research, framework-ventures, hashkey-capital, huobi-ventures, pantera, sevenx-ventures</t>
         </is>
       </c>
       <c r="M28" s="7" t="inlineStr">
@@ -25120,11 +25120,11 @@
         <v>1</v>
       </c>
       <c r="K29" s="6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L29" s="5" t="inlineStr">
         <is>
-          <t>framework-ventures, pantera, polychain</t>
+          <t>cms-holdings, framework-ventures, iosg-ventures, pantera, polychain</t>
         </is>
       </c>
       <c r="M29" s="7" t="inlineStr">
@@ -25183,11 +25183,11 @@
         <v>2</v>
       </c>
       <c r="K30" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L30" s="5" t="inlineStr">
         <is>
-          <t>coinbase-ventures, framework-ventures, pantera</t>
+          <t>coinbase-ventures, digital-currency-group, framework-ventures, pantera</t>
         </is>
       </c>
       <c r="M30" s="7" t="inlineStr">
@@ -25246,11 +25246,11 @@
         <v>1</v>
       </c>
       <c r="K31" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L31" s="5" t="inlineStr">
         <is>
-          <t>electric-capital, framework-ventures, gnosis-vc</t>
+          <t>electric-capital, framework-ventures, gnosis-vc, parafi-capital</t>
         </is>
       </c>
       <c r="M31" s="7" t="inlineStr">
@@ -25309,11 +25309,11 @@
         <v>2</v>
       </c>
       <c r="K32" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L32" s="5" t="inlineStr">
         <is>
-          <t>bain-capital-crypto, coinbase-ventures, framework-ventures, pantera</t>
+          <t>bain-capital-crypto, coinbase-ventures, digital-currency-group, framework-ventures, pantera</t>
         </is>
       </c>
       <c r="M32" s="7" t="inlineStr">
@@ -25368,11 +25368,11 @@
         <v>0</v>
       </c>
       <c r="K33" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L33" s="5" t="inlineStr">
         <is>
-          <t>framework-ventures, maven11</t>
+          <t>framework-ventures, gsr, maven11</t>
         </is>
       </c>
       <c r="M33" s="7" t="inlineStr">
@@ -25490,11 +25490,11 @@
         <v>2</v>
       </c>
       <c r="K35" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L35" s="5" t="inlineStr">
         <is>
-          <t>framework-ventures</t>
+          <t>framework-ventures, iosg-ventures</t>
         </is>
       </c>
       <c r="M35" s="7" t="inlineStr">
@@ -25553,11 +25553,11 @@
         <v>0</v>
       </c>
       <c r="K36" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L36" s="5" t="inlineStr">
         <is>
-          <t>framework-ventures, robot-ventures</t>
+          <t>alliance-dao, framework-ventures, parafi-capital, robot-ventures</t>
         </is>
       </c>
       <c r="M36" s="7" t="inlineStr">
@@ -25616,11 +25616,11 @@
         <v>2</v>
       </c>
       <c r="K37" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L37" s="5" t="inlineStr">
         <is>
-          <t>framework-ventures, robot-ventures</t>
+          <t>alliance-dao, framework-ventures, parafi-capital, robot-ventures</t>
         </is>
       </c>
       <c r="M37" s="7" t="inlineStr">
@@ -25679,11 +25679,11 @@
         <v>0</v>
       </c>
       <c r="K38" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L38" s="5" t="inlineStr">
         <is>
-          <t>framework-ventures, maven11</t>
+          <t>framework-ventures, maven11, mechanism-capital, spartan-group</t>
         </is>
       </c>
       <c r="M38" s="7" t="inlineStr">
@@ -25740,11 +25740,11 @@
         <v>1</v>
       </c>
       <c r="K39" s="6" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="L39" s="5" t="inlineStr">
         <is>
-          <t>framework-ventures</t>
+          <t>fenbushi-capital, framework-ventures, hashkey-capital, huobi-ventures, longhash-ventures, mechanism-capital, okx-ventures, sevenx-ventures</t>
         </is>
       </c>
       <c r="M39" s="7" t="inlineStr">
@@ -25805,11 +25805,11 @@
         <v>0</v>
       </c>
       <c r="K40" s="6" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L40" s="5" t="inlineStr">
         <is>
-          <t>coinbase-ventures, delphi-ventures, framework-ventures</t>
+          <t>alliance-dao, coinbase-ventures, delphi-ventures, framework-ventures, hypersphere, parafi-capital</t>
         </is>
       </c>
       <c r="M40" s="7" t="inlineStr">
@@ -25868,11 +25868,11 @@
         <v>2</v>
       </c>
       <c r="K41" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L41" s="5" t="inlineStr">
         <is>
-          <t>dragonfly, framework-ventures</t>
+          <t>alliance-dao, dragonfly, framework-ventures, longhash-ventures</t>
         </is>
       </c>
       <c r="M41" s="7" t="inlineStr">
@@ -25990,11 +25990,11 @@
         <v>1</v>
       </c>
       <c r="K43" s="6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L43" s="5" t="inlineStr">
         <is>
-          <t>framework-ventures, maven11, multicoin-capital</t>
+          <t>blockchain-capital, cmt-digital, framework-ventures, maven11, multicoin-capital</t>
         </is>
       </c>
       <c r="M43" s="7" t="inlineStr">
@@ -26238,11 +26238,11 @@
         <v>0</v>
       </c>
       <c r="K47" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L47" s="5" t="inlineStr">
         <is>
-          <t>delphi-ventures, framework-ventures</t>
+          <t>alameda-research, cms-holdings, delphi-ventures, framework-ventures</t>
         </is>
       </c>
       <c r="M47" s="7" t="inlineStr">
@@ -26549,11 +26549,11 @@
         <v>0</v>
       </c>
       <c r="K52" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L52" s="5" t="inlineStr">
         <is>
-          <t>coinbase-ventures, framework-ventures</t>
+          <t>alliance-dao, coinbase-ventures, framework-ventures, longhash-ventures</t>
         </is>
       </c>
       <c r="M52" s="7" t="inlineStr">
@@ -26675,11 +26675,11 @@
         <v>1</v>
       </c>
       <c r="K54" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L54" s="5" t="inlineStr">
         <is>
-          <t>coinbase-ventures, framework-ventures, robot-ventures</t>
+          <t>amber-group, coinbase-ventures, framework-ventures, robot-ventures</t>
         </is>
       </c>
       <c r="M54" s="7" t="inlineStr">
@@ -26734,11 +26734,11 @@
         <v>0</v>
       </c>
       <c r="K55" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L55" s="5" t="inlineStr">
         <is>
-          <t>framework-ventures</t>
+          <t>animoca-brands, animoca-brands-japan, framework-ventures</t>
         </is>
       </c>
       <c r="M55" s="7" t="inlineStr">
@@ -26915,11 +26915,11 @@
         <v>0</v>
       </c>
       <c r="K58" s="6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L58" s="5" t="inlineStr">
         <is>
-          <t>framework-ventures, pantera</t>
+          <t>alameda-research, framework-ventures, iosg-ventures, pantera, spartan-group</t>
         </is>
       </c>
       <c r="M58" s="7" t="inlineStr">
@@ -27041,11 +27041,11 @@
         <v>1</v>
       </c>
       <c r="K60" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L60" s="5" t="inlineStr">
         <is>
-          <t>framework-ventures, maven11</t>
+          <t>blockchain-capital, framework-ventures, maven11, parafi-capital</t>
         </is>
       </c>
       <c r="M60" s="7" t="inlineStr">
@@ -27230,11 +27230,11 @@
         <v>1</v>
       </c>
       <c r="K63" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L63" s="5" t="inlineStr">
         <is>
-          <t>framework-ventures, lemniscap</t>
+          <t>framework-ventures, gsr, lemniscap</t>
         </is>
       </c>
       <c r="M63" s="7" t="inlineStr">
@@ -27295,11 +27295,11 @@
         <v>0</v>
       </c>
       <c r="K64" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L64" s="5" t="inlineStr">
         <is>
-          <t>framework-ventures</t>
+          <t>framework-ventures, iosg-ventures</t>
         </is>
       </c>
       <c r="M64" s="7" t="inlineStr">
@@ -27358,11 +27358,11 @@
         <v>3</v>
       </c>
       <c r="K65" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L65" s="5" t="inlineStr">
         <is>
-          <t>framework-ventures</t>
+          <t>arrington-capital, framework-ventures, jump-crypto</t>
         </is>
       </c>
       <c r="M65" s="7" t="inlineStr">
@@ -27421,11 +27421,11 @@
         <v>1</v>
       </c>
       <c r="K66" s="6" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L66" s="5" t="inlineStr">
         <is>
-          <t>delphi-ventures, framework-ventures, polychain</t>
+          <t>blockchain-capital, coinfund, delphi-ventures, framework-ventures, mechanism-capital, polychain</t>
         </is>
       </c>
       <c r="M66" s="7" t="inlineStr">
@@ -27484,11 +27484,11 @@
         <v>0</v>
       </c>
       <c r="K67" s="6" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L67" s="5" t="inlineStr">
         <is>
-          <t>delphi-ventures, framework-ventures, polychain</t>
+          <t>blockchain-capital, coinfund, delphi-ventures, framework-ventures, mechanism-capital, polychain</t>
         </is>
       </c>
       <c r="M67" s="7" t="inlineStr">
@@ -27610,11 +27610,11 @@
         <v>0</v>
       </c>
       <c r="K69" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L69" s="5" t="inlineStr">
         <is>
-          <t>delphi-ventures, framework-ventures</t>
+          <t>delphi-ventures, framework-ventures, iosg-ventures</t>
         </is>
       </c>
       <c r="M69" s="7" t="inlineStr">
@@ -27856,11 +27856,11 @@
         <v>2</v>
       </c>
       <c r="K73" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L73" s="5" t="inlineStr">
         <is>
-          <t>electric-capital, framework-ventures</t>
+          <t>electric-capital, framework-ventures, gsr</t>
         </is>
       </c>
       <c r="M73" s="7" t="inlineStr">
@@ -27919,11 +27919,11 @@
         <v>0</v>
       </c>
       <c r="K74" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L74" s="5" t="inlineStr">
         <is>
-          <t>framework-ventures, pantera</t>
+          <t>animoca-brands, framework-ventures, pantera</t>
         </is>
       </c>
       <c r="M74" s="7" t="inlineStr">
@@ -27982,11 +27982,11 @@
         <v>4</v>
       </c>
       <c r="K75" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L75" s="5" t="inlineStr">
         <is>
-          <t>framework-ventures</t>
+          <t>framework-ventures, hypersphere</t>
         </is>
       </c>
       <c r="M75" s="7" t="inlineStr">
@@ -28045,11 +28045,11 @@
         <v>4</v>
       </c>
       <c r="K76" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L76" s="5" t="inlineStr">
         <is>
-          <t>framework-ventures</t>
+          <t>framework-ventures, hypersphere</t>
         </is>
       </c>
       <c r="M76" s="10" t="n"/>
@@ -28102,11 +28102,11 @@
         <v>0</v>
       </c>
       <c r="K77" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L77" s="5" t="inlineStr">
         <is>
-          <t>framework-ventures, pantera</t>
+          <t>blockchain-capital, framework-ventures, pantera</t>
         </is>
       </c>
       <c r="M77" s="7" t="inlineStr">
@@ -28165,11 +28165,11 @@
         <v>0</v>
       </c>
       <c r="K78" s="6" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L78" s="5" t="inlineStr">
         <is>
-          <t>coinbase-ventures, electric-capital, framework-ventures, lemniscap</t>
+          <t>coinbase-ventures, coinfund, electric-capital, framework-ventures, galaxy-digital, jump-crypto, lemniscap</t>
         </is>
       </c>
       <c r="M78" s="7" t="inlineStr">
@@ -28228,11 +28228,11 @@
         <v>0</v>
       </c>
       <c r="K79" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L79" s="5" t="inlineStr">
         <is>
-          <t>framework-ventures, multicoin-capital</t>
+          <t>blockchain-capital, framework-ventures, multicoin-capital</t>
         </is>
       </c>
       <c r="M79" s="7" t="inlineStr">
@@ -28476,11 +28476,11 @@
         <v>1</v>
       </c>
       <c r="K83" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L83" s="5" t="inlineStr">
         <is>
-          <t>coinbase-ventures, framework-ventures</t>
+          <t>coinbase-ventures, framework-ventures, hypersphere</t>
         </is>
       </c>
       <c r="M83" s="7" t="inlineStr">
@@ -28535,11 +28535,11 @@
         <v>1</v>
       </c>
       <c r="K84" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L84" s="5" t="inlineStr">
         <is>
-          <t>coinbase-ventures, framework-ventures</t>
+          <t>circle-ventures, coinbase-ventures, framework-ventures, hypersphere</t>
         </is>
       </c>
       <c r="M84" s="7" t="inlineStr">
@@ -28598,11 +28598,11 @@
         <v>1</v>
       </c>
       <c r="K85" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L85" s="5" t="inlineStr">
         <is>
-          <t>framework-ventures</t>
+          <t>framework-ventures, mirana-ventures, polygon-ventures, sfermion, spartan-group</t>
         </is>
       </c>
       <c r="M85" s="7" t="inlineStr">
@@ -28661,11 +28661,11 @@
         <v>1</v>
       </c>
       <c r="K86" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L86" s="5" t="inlineStr">
         <is>
-          <t>framework-ventures</t>
+          <t>alliance-dao, digital-currency-group, foresight-ventures, framework-ventures, iosg-ventures</t>
         </is>
       </c>
       <c r="M86" s="7" t="inlineStr">
@@ -28724,11 +28724,11 @@
         <v>0</v>
       </c>
       <c r="K87" s="6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L87" s="5" t="inlineStr">
         <is>
-          <t>delphi-ventures, framework-ventures, multicoin-capital, robot-ventures</t>
+          <t>alameda-research, delphi-ventures, framework-ventures, multicoin-capital, robot-ventures, solana-ventures</t>
         </is>
       </c>
       <c r="M87" s="7" t="inlineStr">
@@ -28787,11 +28787,11 @@
         <v>0</v>
       </c>
       <c r="K88" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L88" s="5" t="inlineStr">
         <is>
-          <t>framework-ventures, multicoin-capital</t>
+          <t>framework-ventures, hashed, multicoin-capital, solana-ventures</t>
         </is>
       </c>
       <c r="M88" s="7" t="inlineStr">
@@ -28850,11 +28850,11 @@
         <v>0</v>
       </c>
       <c r="K89" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L89" s="5" t="inlineStr">
         <is>
-          <t>framework-ventures</t>
+          <t>coinfund, framework-ventures</t>
         </is>
       </c>
       <c r="M89" s="7" t="inlineStr">
@@ -28909,11 +28909,11 @@
         <v>0</v>
       </c>
       <c r="K90" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L90" s="5" t="inlineStr">
         <is>
-          <t>coinbase-ventures, framework-ventures, polychain</t>
+          <t>circle-ventures, coinbase-ventures, framework-ventures, polychain</t>
         </is>
       </c>
       <c r="M90" s="7" t="inlineStr">
@@ -28972,11 +28972,11 @@
         <v>0</v>
       </c>
       <c r="K91" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L91" s="5" t="inlineStr">
         <is>
-          <t>electric-capital, framework-ventures</t>
+          <t>electric-capital, framework-ventures, polygon-ventures</t>
         </is>
       </c>
       <c r="M91" s="7" t="inlineStr">
@@ -29157,11 +29157,11 @@
         <v>0</v>
       </c>
       <c r="K94" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L94" s="5" t="inlineStr">
         <is>
-          <t>framework-ventures</t>
+          <t>foresight-ventures, framework-ventures, gsr</t>
         </is>
       </c>
       <c r="M94" s="7" t="inlineStr">
@@ -29283,11 +29283,11 @@
         <v>0</v>
       </c>
       <c r="K96" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L96" s="5" t="inlineStr">
         <is>
-          <t>framework-ventures</t>
+          <t>framework-ventures, polygon-ventures, sevenx-ventures</t>
         </is>
       </c>
       <c r="M96" s="7" t="inlineStr">
@@ -29346,11 +29346,11 @@
         <v>0</v>
       </c>
       <c r="K97" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L97" s="5" t="inlineStr">
         <is>
-          <t>framework-ventures</t>
+          <t>animoca-brands, framework-ventures</t>
         </is>
       </c>
       <c r="M97" s="7" t="inlineStr">
@@ -29409,11 +29409,11 @@
         <v>1</v>
       </c>
       <c r="K98" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L98" s="5" t="inlineStr">
         <is>
-          <t>framework-ventures</t>
+          <t>blockchain-capital, framework-ventures</t>
         </is>
       </c>
       <c r="M98" s="7" t="inlineStr">
@@ -29535,11 +29535,11 @@
         <v>0</v>
       </c>
       <c r="K100" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L100" s="5" t="inlineStr">
         <is>
-          <t>framework-ventures</t>
+          <t>framework-ventures, gsr</t>
         </is>
       </c>
       <c r="M100" s="7" t="inlineStr">
@@ -29598,11 +29598,11 @@
         <v>0</v>
       </c>
       <c r="K101" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L101" s="5" t="inlineStr">
         <is>
-          <t>framework-ventures</t>
+          <t>framework-ventures, iosg-ventures</t>
         </is>
       </c>
       <c r="M101" s="7" t="inlineStr">
@@ -29968,11 +29968,11 @@
         <v>1</v>
       </c>
       <c r="K107" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L107" s="5" t="inlineStr">
         <is>
-          <t>coinbase-ventures, framework-ventures</t>
+          <t>circle-ventures, coinbase-ventures, framework-ventures, spartan-group</t>
         </is>
       </c>
       <c r="M107" s="7" t="inlineStr">
@@ -30031,11 +30031,11 @@
         <v>1</v>
       </c>
       <c r="K108" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L108" s="5" t="inlineStr">
         <is>
-          <t>framework-ventures</t>
+          <t>framework-ventures, polygon-ventures</t>
         </is>
       </c>
       <c r="M108" s="7" t="inlineStr">
@@ -30210,11 +30210,11 @@
         <v>1</v>
       </c>
       <c r="K111" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L111" s="5" t="inlineStr">
         <is>
-          <t>framework-ventures, robot-ventures</t>
+          <t>1kx, framework-ventures, robot-ventures</t>
         </is>
       </c>
       <c r="M111" s="7" t="inlineStr">
@@ -30273,11 +30273,11 @@
         <v>2</v>
       </c>
       <c r="K112" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L112" s="5" t="inlineStr">
         <is>
-          <t>framework-ventures, maven11</t>
+          <t>framework-ventures, maven11, spartan-group</t>
         </is>
       </c>
       <c r="M112" s="7" t="inlineStr">
@@ -30462,11 +30462,11 @@
         <v>0</v>
       </c>
       <c r="K115" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L115" s="5" t="inlineStr">
         <is>
-          <t>electric-capital, framework-ventures</t>
+          <t>electric-capital, framework-ventures, gsr, jump-crypto</t>
         </is>
       </c>
       <c r="M115" s="7" t="inlineStr">
@@ -30519,11 +30519,11 @@
         <v>0</v>
       </c>
       <c r="K116" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L116" s="5" t="inlineStr">
         <is>
-          <t>framework-ventures</t>
+          <t>framework-ventures, galaxy-digital</t>
         </is>
       </c>
       <c r="M116" s="7" t="inlineStr">
@@ -30643,11 +30643,11 @@
         <v>2</v>
       </c>
       <c r="K118" s="6" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L118" s="5" t="inlineStr">
         <is>
-          <t>framework-ventures, polychain</t>
+          <t>framework-ventures, hack-vc, iosg-ventures, okx-ventures, polychain, polygon-ventures</t>
         </is>
       </c>
       <c r="M118" s="7" t="inlineStr">
@@ -30706,11 +30706,11 @@
         <v>1</v>
       </c>
       <c r="K119" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L119" s="5" t="inlineStr">
         <is>
-          <t>coinbase-ventures, framework-ventures, pantera</t>
+          <t>coinbase-ventures, digital-currency-group, framework-ventures, pantera</t>
         </is>
       </c>
       <c r="M119" s="7" t="inlineStr">
@@ -30765,11 +30765,11 @@
         <v>1</v>
       </c>
       <c r="K120" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L120" s="5" t="inlineStr">
         <is>
-          <t>framework-ventures</t>
+          <t>framework-ventures, sevenx-ventures</t>
         </is>
       </c>
       <c r="M120" s="7" t="inlineStr">
@@ -30828,11 +30828,11 @@
         <v>0</v>
       </c>
       <c r="K121" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L121" s="5" t="inlineStr">
         <is>
-          <t>framework-ventures</t>
+          <t>fenbushi-capital, framework-ventures, mechanism-capital</t>
         </is>
       </c>
       <c r="M121" s="7" t="inlineStr">
@@ -30893,11 +30893,11 @@
         <v>0</v>
       </c>
       <c r="K122" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L122" s="5" t="inlineStr">
         <is>
-          <t>coinbase-ventures, framework-ventures, pantera</t>
+          <t>coinbase-ventures, digital-currency-group, framework-ventures, pantera</t>
         </is>
       </c>
       <c r="M122" s="7" t="inlineStr">
@@ -30958,11 +30958,11 @@
         <v>2</v>
       </c>
       <c r="K123" s="6" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="L123" s="5" t="inlineStr">
         <is>
-          <t>framework-ventures, polychain</t>
+          <t>amber-group, animoca-brands, arrington-capital, framework-ventures, hack-vc, hashkey-capital, hypersphere, polychain, spartan-group</t>
         </is>
       </c>
       <c r="M123" s="7" t="inlineStr">
@@ -31021,11 +31021,11 @@
         <v>2</v>
       </c>
       <c r="K124" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L124" s="5" t="inlineStr">
         <is>
-          <t>framework-ventures</t>
+          <t>big-brain-holdings, framework-ventures</t>
         </is>
       </c>
       <c r="M124" s="7" t="inlineStr">
@@ -31084,11 +31084,11 @@
         <v>0</v>
       </c>
       <c r="K125" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L125" s="5" t="inlineStr">
         <is>
-          <t>framework-ventures</t>
+          <t>circle-ventures, framework-ventures</t>
         </is>
       </c>
       <c r="M125" s="7" t="inlineStr">
@@ -31143,11 +31143,11 @@
         <v>0</v>
       </c>
       <c r="K126" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L126" s="5" t="inlineStr">
         <is>
-          <t>coinbase-ventures, framework-ventures, robot-ventures</t>
+          <t>amber-group, coinbase-ventures, framework-ventures, robot-ventures</t>
         </is>
       </c>
       <c r="M126" s="7" t="inlineStr">
@@ -31206,11 +31206,11 @@
         <v>2</v>
       </c>
       <c r="K127" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L127" s="5" t="inlineStr">
         <is>
-          <t>framework-ventures</t>
+          <t>alliance-dao, framework-ventures, okx-ventures</t>
         </is>
       </c>
       <c r="M127" s="7" t="inlineStr">
@@ -31265,11 +31265,11 @@
         <v>3</v>
       </c>
       <c r="K128" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L128" s="5" t="inlineStr">
         <is>
-          <t>coinbase-ventures, framework-ventures</t>
+          <t>coinbase-ventures, framework-ventures, gsr, hack-vc</t>
         </is>
       </c>
       <c r="M128" s="7" t="inlineStr">
@@ -31513,11 +31513,11 @@
         <v>1</v>
       </c>
       <c r="K132" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L132" s="5" t="inlineStr">
         <is>
-          <t>framework-ventures, lemniscap</t>
+          <t>framework-ventures, hypersphere, lemniscap</t>
         </is>
       </c>
       <c r="M132" s="10" t="n"/>
@@ -31572,11 +31572,11 @@
         <v>3</v>
       </c>
       <c r="K133" s="6" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="L133" s="5" t="inlineStr">
         <is>
-          <t>delphi-ventures, founders-fund, framework-ventures, pantera, robot-ventures</t>
+          <t>arrington-capital, delphi-ventures, foresight-ventures, founders-fund, framework-ventures, hack-vc, hashkey-capital, hypersphere, mh-ventures, mirana-ventures, pantera, robot-ventures, spartan-group</t>
         </is>
       </c>
       <c r="M133" s="7" t="inlineStr">
@@ -31635,11 +31635,11 @@
         <v>2</v>
       </c>
       <c r="K134" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L134" s="5" t="inlineStr">
         <is>
-          <t>framework-ventures</t>
+          <t>framework-ventures, mechanism-capital, mh-ventures</t>
         </is>
       </c>
       <c r="M134" s="7" t="inlineStr">
@@ -31820,11 +31820,11 @@
         <v>1</v>
       </c>
       <c r="K137" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L137" s="5" t="inlineStr">
         <is>
-          <t>framework-ventures</t>
+          <t>framework-ventures, parafi-capital</t>
         </is>
       </c>
       <c r="M137" s="7" t="inlineStr">
@@ -31883,11 +31883,11 @@
         <v>1</v>
       </c>
       <c r="K138" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L138" s="5" t="inlineStr">
         <is>
-          <t>framework-ventures, polychain</t>
+          <t>framework-ventures, huobi-ventures, polychain, yzi-labs</t>
         </is>
       </c>
       <c r="M138" s="7" t="inlineStr">
@@ -31946,11 +31946,11 @@
         <v>4</v>
       </c>
       <c r="K139" s="6" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L139" s="5" t="inlineStr">
         <is>
-          <t>framework-ventures</t>
+          <t>arrington-capital, circle-ventures, digital-currency-group, framework-ventures, mh-ventures, okx-ventures</t>
         </is>
       </c>
       <c r="M139" s="7" t="inlineStr">
@@ -32009,11 +32009,11 @@
         <v>2</v>
       </c>
       <c r="K140" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L140" s="5" t="inlineStr">
         <is>
-          <t>framework-ventures</t>
+          <t>1kx, framework-ventures</t>
         </is>
       </c>
       <c r="M140" s="7" t="inlineStr">
@@ -32068,11 +32068,11 @@
         <v>2</v>
       </c>
       <c r="K141" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L141" s="5" t="inlineStr">
         <is>
-          <t>framework-ventures</t>
+          <t>big-brain-holdings, framework-ventures</t>
         </is>
       </c>
       <c r="M141" s="7" t="inlineStr">
@@ -32190,11 +32190,11 @@
         <v>0</v>
       </c>
       <c r="K143" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L143" s="5" t="inlineStr">
         <is>
-          <t>cyber-fund, founders-fund, framework-ventures</t>
+          <t>cyber-fund, founders-fund, framework-ventures, solana-ventures</t>
         </is>
       </c>
       <c r="M143" s="7" t="inlineStr">
@@ -32623,11 +32623,11 @@
         <v>1</v>
       </c>
       <c r="K150" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L150" s="5" t="inlineStr">
         <is>
-          <t>framework-ventures</t>
+          <t>framework-ventures, solana-ventures</t>
         </is>
       </c>
       <c r="M150" s="7" t="inlineStr">
@@ -32686,11 +32686,11 @@
         <v>4</v>
       </c>
       <c r="K151" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L151" s="5" t="inlineStr">
         <is>
-          <t>framework-ventures</t>
+          <t>amber-group, framework-ventures, mirana-ventures, sfermion, spartan-group</t>
         </is>
       </c>
       <c r="M151" s="7" t="inlineStr">
@@ -32871,11 +32871,11 @@
         <v>1</v>
       </c>
       <c r="K154" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L154" s="5" t="inlineStr">
         <is>
-          <t>coinbase-ventures, delphi-ventures, framework-ventures</t>
+          <t>1kx, coinbase-ventures, delphi-ventures, framework-ventures</t>
         </is>
       </c>
       <c r="M154" s="7" t="inlineStr">
@@ -32934,11 +32934,11 @@
         <v>1</v>
       </c>
       <c r="K155" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L155" s="5" t="inlineStr">
         <is>
-          <t>framework-ventures</t>
+          <t>framework-ventures, mirana-ventures</t>
         </is>
       </c>
       <c r="M155" s="7" t="inlineStr">
@@ -33186,11 +33186,11 @@
         <v>0</v>
       </c>
       <c r="K159" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L159" s="5" t="inlineStr">
         <is>
-          <t>framework-ventures</t>
+          <t>framework-ventures, hypersphere</t>
         </is>
       </c>
       <c r="M159" s="7" t="inlineStr">
@@ -33249,11 +33249,11 @@
         <v>1</v>
       </c>
       <c r="K160" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L160" s="5" t="inlineStr">
         <is>
-          <t>framework-ventures</t>
+          <t>arrington-capital, framework-ventures</t>
         </is>
       </c>
       <c r="M160" s="7" t="inlineStr">
@@ -33375,11 +33375,11 @@
         <v>1</v>
       </c>
       <c r="K162" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L162" s="5" t="inlineStr">
         <is>
-          <t>dragonfly, framework-ventures</t>
+          <t>big-brain-holdings, cmt-digital, dragonfly, framework-ventures</t>
         </is>
       </c>
       <c r="M162" s="7" t="inlineStr">
@@ -33737,11 +33737,11 @@
         <v>2</v>
       </c>
       <c r="K168" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L168" s="5" t="inlineStr">
         <is>
-          <t>coinbase-ventures, framework-ventures</t>
+          <t>coinbase-ventures, framework-ventures, gsr</t>
         </is>
       </c>
       <c r="M168" s="7" t="inlineStr">
@@ -33800,11 +33800,11 @@
         <v>0</v>
       </c>
       <c r="K169" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L169" s="5" t="inlineStr">
         <is>
-          <t>framework-ventures</t>
+          <t>framework-ventures, galaxy-digital</t>
         </is>
       </c>
       <c r="M169" s="7" t="inlineStr">
@@ -41240,19 +41240,19 @@
       </c>
       <c r="F2" s="12" t="inlineStr">
         <is>
-          <t>Fondspagina toont een vast maximum aantal regels; dit is een displaylimiet en geen portefeuilletotaal.</t>
+          <t>The fund page shows a fixed maximum number of rows; this is a display limit, not a portfolio total.</t>
         </is>
       </c>
       <c r="G2" s="6" t="n"/>
       <c r="H2" s="12" t="inlineStr">
         <is>
-          <t>Pagina levert geen leesbare portefeuillelijst in statische HTML (client-side gerenderd). Niet geteld; geen schatting gemaakt.</t>
+          <t>Page delivers no readable portfolio list in static HTML (client-side rendered). Not counted; no estimate made.</t>
         </is>
       </c>
       <c r="I2" s="6" t="n"/>
       <c r="J2" s="12" t="inlineStr">
         <is>
-          <t>Geen telling verkregen; niet geschat.</t>
+          <t>No count obtained; not estimated.</t>
         </is>
       </c>
       <c r="K2" s="6" t="n">
@@ -41260,7 +41260,7 @@
       </c>
       <c r="L2" s="12" t="inlineStr">
         <is>
-          <t>`investments` is CryptoRanks eigen telling. De zichtbare portefeuillelijst toont zonder account maar tien regels; die lijst is niet gebruikt.</t>
+          <t>`investments` is CryptoRank's own count. The visible portfolio list shows only ten rows without an account; that list was not used.</t>
         </is>
       </c>
       <c r="M2" s="6" t="n">
